--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E001AC8-4639-7441-8E31-8E047439F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A4E7AD-8225-5C44-90D7-BD44681FBA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="15000" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cartoline" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="85">
   <si>
     <t>titolo</t>
   </si>
@@ -76,9 +76,6 @@
     <t>La vista su Positano alla fine del sentiero degli Dei è spettacolare</t>
   </si>
   <si>
-    <t>limone</t>
-  </si>
-  <si>
     <t>IMG_9743.JPG</t>
   </si>
   <si>
@@ -122,13 +119,169 @@
   </si>
   <si>
     <t>IMG_2162.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9684.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9685.JPG</t>
+  </si>
+  <si>
+    <t>Il Faro</t>
+  </si>
+  <si>
+    <t>IMG_9690.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9686.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9687.JPG</t>
+  </si>
+  <si>
+    <t>Tuffo a mare</t>
+  </si>
+  <si>
+    <t>IMG_9694.JPG</t>
+  </si>
+  <si>
+    <t>Gioventù</t>
+  </si>
+  <si>
+    <t>IMG_9691.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9696.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9699.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9701.JPG</t>
+  </si>
+  <si>
+    <t>Partenope</t>
+  </si>
+  <si>
+    <t>IMG_9704.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9707.JPG</t>
+  </si>
+  <si>
+    <t>Tramonto su Ischia</t>
+  </si>
+  <si>
+    <t>IMG_9710.JPG</t>
+  </si>
+  <si>
+    <t>vesuvio</t>
+  </si>
+  <si>
+    <t>Turisti in viaggio</t>
+  </si>
+  <si>
+    <t>IMG_9711.JPG</t>
+  </si>
+  <si>
+    <t>Il traghetto nel golfo</t>
+  </si>
+  <si>
+    <t>IMG_9692.JPG</t>
+  </si>
+  <si>
+    <t>Maya!</t>
+  </si>
+  <si>
+    <t>IMG_9693.JPG</t>
+  </si>
+  <si>
+    <t>Il covo di Tato</t>
+  </si>
+  <si>
+    <t>IMG_9713.JPG</t>
+  </si>
+  <si>
+    <t>La terrazza di Surrient</t>
+  </si>
+  <si>
+    <t>Sorrento</t>
+  </si>
+  <si>
+    <t>limoni</t>
+  </si>
+  <si>
+    <t>IMG_9714.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9715.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9718.JPG</t>
+  </si>
+  <si>
+    <t>La piscina della Regina</t>
+  </si>
+  <si>
+    <t>Bagni Regina Giovanna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorrento </t>
+  </si>
+  <si>
+    <t>IMG_9721.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9723.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9725.JPG</t>
+  </si>
+  <si>
+    <t>Sugli scogli</t>
+  </si>
+  <si>
+    <t>IMG_9728.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9732.JPG</t>
+  </si>
+  <si>
+    <t>Checco e Dani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costiera Amalfitana </t>
+  </si>
+  <si>
+    <t>Il casolare sulla Costiera</t>
+  </si>
+  <si>
+    <t>IMG_9733.JPG</t>
+  </si>
+  <si>
+    <t>Il Sentiero degli Dei</t>
+  </si>
+  <si>
+    <t>IMG_9735.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9736.JPG</t>
+  </si>
+  <si>
+    <t>Vista sul Sentiero</t>
+  </si>
+  <si>
+    <t>IMG_9739.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9741.JPG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
@@ -147,6 +300,11 @@
     <font>
       <sz val="12"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -522,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -588,7 +746,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
@@ -597,82 +755,644 @@
         <v>17</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A4E7AD-8225-5C44-90D7-BD44681FBA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB2E88C-D263-114B-90D7-91390A5A830C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cartoline" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="153">
   <si>
     <t>titolo</t>
   </si>
@@ -275,6 +275,210 @@
   </si>
   <si>
     <t>IMG_9741.JPG</t>
+  </si>
+  <si>
+    <t>IMG_4133.jpg</t>
+  </si>
+  <si>
+    <t>istanbul</t>
+  </si>
+  <si>
+    <t>Istanbul</t>
+  </si>
+  <si>
+    <t>IMG_4137.jpg</t>
+  </si>
+  <si>
+    <t>Moschea Blu</t>
+  </si>
+  <si>
+    <t>moschea</t>
+  </si>
+  <si>
+    <t>IMG_4138.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4149.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4152.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4156.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4162.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4165.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4168.jpg</t>
+  </si>
+  <si>
+    <t>Santa Sofia</t>
+  </si>
+  <si>
+    <t>IMG_4173.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4181.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4188.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4193.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4196.jpg</t>
+  </si>
+  <si>
+    <t>Venditore di Tappeti</t>
+  </si>
+  <si>
+    <t>IMG_4197.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4199.jpg</t>
+  </si>
+  <si>
+    <t>Cena Turca!</t>
+  </si>
+  <si>
+    <t>IMG_4204.jpg</t>
+  </si>
+  <si>
+    <t>La Moschea illuminata</t>
+  </si>
+  <si>
+    <t>IMG_4206.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4207.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4209.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4226.jpg</t>
+  </si>
+  <si>
+    <t>Labirinto di Colonne</t>
+  </si>
+  <si>
+    <t>Basilica cisterna</t>
+  </si>
+  <si>
+    <t>Hagia Sofia</t>
+  </si>
+  <si>
+    <t>Testa di Medusa</t>
+  </si>
+  <si>
+    <t>IMG_4237.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4257.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4266.jpg</t>
+  </si>
+  <si>
+    <t>Torre di Galata</t>
+  </si>
+  <si>
+    <t>Galata</t>
+  </si>
+  <si>
+    <t>IMG_4269.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4274.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4278.jpg</t>
+  </si>
+  <si>
+    <t>Come to Galatasaray</t>
+  </si>
+  <si>
+    <t>IMG_4296.jpg</t>
+  </si>
+  <si>
+    <t>No pictures!</t>
+  </si>
+  <si>
+    <t>IMG_4299.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4302.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4303.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4313.jpg</t>
+  </si>
+  <si>
+    <t>Gatto turco</t>
+  </si>
+  <si>
+    <t>IMG_4314.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4329.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4330.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4337.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4342.jpg</t>
+  </si>
+  <si>
+    <t>Bazar delle Spezie</t>
+  </si>
+  <si>
+    <t>IMG_4347.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4354.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4356.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4370.jpg</t>
+  </si>
+  <si>
+    <t>Mezzaluna e la stella</t>
+  </si>
+  <si>
+    <t>IMG_4376.jpg</t>
+  </si>
+  <si>
+    <t>Pesca nello stretto</t>
+  </si>
+  <si>
+    <t>IMG_4379.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4380.jpg</t>
+  </si>
+  <si>
+    <t>IMG_4382.jpg</t>
+  </si>
+  <si>
+    <t>L'ingresso del Bazar</t>
+  </si>
+  <si>
+    <t>IMG_4392.jpg</t>
+  </si>
+  <si>
+    <t>Il Sultano</t>
   </si>
 </sst>
 </file>
@@ -680,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -1391,6 +1595,836 @@
         <v>84</v>
       </c>
     </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B41" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B42" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B43" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B44" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B46" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B48" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B51" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B54" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B55" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B56" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B59" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B61" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B62" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B65" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B66" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B67" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B69" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B70" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B71" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B72" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B74" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B75" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B76" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B79" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB2E88C-D263-114B-90D7-91390A5A830C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F807FF9E-5768-844A-BDE4-CA7E3D45BC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cartoline" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="188">
   <si>
     <t>titolo</t>
   </si>
@@ -479,6 +479,111 @@
   </si>
   <si>
     <t>Il Sultano</t>
+  </si>
+  <si>
+    <t>IMG_9857.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9861.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9863.JPG</t>
+  </si>
+  <si>
+    <t>IMG_9866.JPG</t>
+  </si>
+  <si>
+    <t>Il ponte sul fiordo</t>
+  </si>
+  <si>
+    <t>Fiordo di Furore</t>
+  </si>
+  <si>
+    <t>IMG_0669.JPG</t>
+  </si>
+  <si>
+    <t>Terrazza su Capri</t>
+  </si>
+  <si>
+    <t>Termini</t>
+  </si>
+  <si>
+    <t>IMG_0672.JPG</t>
+  </si>
+  <si>
+    <t>Il bar del paese</t>
+  </si>
+  <si>
+    <t>IMG_0677.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0678 2.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0681.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0682</t>
+  </si>
+  <si>
+    <t>IMG_0688.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0690.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0694.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0698.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0704.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0706.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0716 2.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0717.JPG</t>
+  </si>
+  <si>
+    <t>Baia delle Sirene</t>
+  </si>
+  <si>
+    <t>Baia di Ieranto</t>
+  </si>
+  <si>
+    <t>Punta Campanella</t>
+  </si>
+  <si>
+    <t>IMG_0718.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0723.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0726.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0727.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0730.JPG</t>
+  </si>
+  <si>
+    <t>Miez' o' Mar</t>
+  </si>
+  <si>
+    <t>IMG_0734.JPG</t>
+  </si>
+  <si>
+    <t>IMG_0739.JPG</t>
+  </si>
+  <si>
+    <t>ottobre 2025</t>
   </si>
 </sst>
 </file>
@@ -884,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -2425,6 +2530,446 @@
         <v>151</v>
       </c>
     </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B83" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B85" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B90" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B91" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B92" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B93" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B94" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B95" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B96" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B97" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B98" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B100" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B101" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B102" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B103" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B104" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B106" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B107" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F807FF9E-5768-844A-BDE4-CA7E3D45BC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFBEA72-F29A-1E4E-9E13-84C661031942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="286">
   <si>
     <t>titolo</t>
   </si>
@@ -584,6 +584,300 @@
   </si>
   <si>
     <t>ottobre 2025</t>
+  </si>
+  <si>
+    <t>sirena</t>
+  </si>
+  <si>
+    <t>IMG_5830.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5833.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5838.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5844.JPG</t>
+  </si>
+  <si>
+    <t>Natale e Maradona</t>
+  </si>
+  <si>
+    <t>dicembre 2025</t>
+  </si>
+  <si>
+    <t>IMG_5848.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5852.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5863.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5868.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5869.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5873.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5882.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5883.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5893.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5896.JPG</t>
+  </si>
+  <si>
+    <t>Università della Strada</t>
+  </si>
+  <si>
+    <t>IMG_5898.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5901.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5903.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5905.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5906.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5907.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5912.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5914.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5918.JPG</t>
+  </si>
+  <si>
+    <t>Stai mman all'arte</t>
+  </si>
+  <si>
+    <t>IMG_5920.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5921.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5928.JPG</t>
+  </si>
+  <si>
+    <t>Sacro e Profano</t>
+  </si>
+  <si>
+    <t>IMG_5932.JPG</t>
+  </si>
+  <si>
+    <t>San Gennà</t>
+  </si>
+  <si>
+    <t>IMG_5939.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5943.JPG</t>
+  </si>
+  <si>
+    <t>Arte Presepiale</t>
+  </si>
+  <si>
+    <t>IMG_5945.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5947.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5948.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5953.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5957.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5959.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5960.JPG</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>IMG_5963.JPG</t>
+  </si>
+  <si>
+    <t>Muri puliti, Popoli muti</t>
+  </si>
+  <si>
+    <t>IMG_5964.JPG</t>
+  </si>
+  <si>
+    <t>Libri scolastici</t>
+  </si>
+  <si>
+    <t>IMG_5965.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5969.JPG</t>
+  </si>
+  <si>
+    <t>Quartieri Spagnoli</t>
+  </si>
+  <si>
+    <t>IMG_5970.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5972.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5978.JPG</t>
+  </si>
+  <si>
+    <t>IMG_5990.JPG</t>
+  </si>
+  <si>
+    <t>D10S</t>
+  </si>
+  <si>
+    <t>IMG_6000.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6009.JPG</t>
+  </si>
+  <si>
+    <t>Napulitan'</t>
+  </si>
+  <si>
+    <t>IMG_6013.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6017.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6018.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6022.JPG</t>
+  </si>
+  <si>
+    <t>Panni stesi</t>
+  </si>
+  <si>
+    <t>IMG_6025.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6032.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6035.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6044.JPG</t>
+  </si>
+  <si>
+    <t>Bene Assaje</t>
+  </si>
+  <si>
+    <t>IMG_6045.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6049.JPG</t>
+  </si>
+  <si>
+    <t>Elemosina</t>
+  </si>
+  <si>
+    <t>IMG_6050.JPG</t>
+  </si>
+  <si>
+    <t>o' cafè</t>
+  </si>
+  <si>
+    <t>IMG_6076.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6078.JPG</t>
+  </si>
+  <si>
+    <t>Plebiscito</t>
+  </si>
+  <si>
+    <t>IMG_6079.JPG</t>
+  </si>
+  <si>
+    <t>Pulcinella</t>
+  </si>
+  <si>
+    <t>IMG_6086.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6089.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6095.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6088.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6102.JPG</t>
+  </si>
+  <si>
+    <t>Dopo-scuola</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>IMG_6109.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6117.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6126.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6150.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6153.JPG</t>
+  </si>
+  <si>
+    <t>o' scalon'</t>
+  </si>
+  <si>
+    <t>o' castell' ngopp o' mar</t>
+  </si>
+  <si>
+    <t>IMG_6158.JPG</t>
+  </si>
+  <si>
+    <t>IMG_6162.JPG</t>
+  </si>
+  <si>
+    <t>Toledo sotto il mare</t>
+  </si>
+  <si>
+    <t>Napoli</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -2652,7 +2946,7 @@
         <v>187</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>164</v>
@@ -2669,7 +2963,7 @@
         <v>187</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>165</v>
@@ -2686,7 +2980,7 @@
         <v>187</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>166</v>
@@ -2703,7 +2997,7 @@
         <v>187</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>167</v>
@@ -2720,7 +3014,7 @@
         <v>187</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>168</v>
@@ -2737,7 +3031,7 @@
         <v>187</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>169</v>
@@ -2754,7 +3048,7 @@
         <v>187</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>170</v>
@@ -2771,7 +3065,7 @@
         <v>187</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>171</v>
@@ -2788,7 +3082,7 @@
         <v>187</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>172</v>
@@ -2805,7 +3099,7 @@
         <v>187</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>173</v>
@@ -2825,7 +3119,7 @@
         <v>187</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>174</v>
@@ -2842,7 +3136,7 @@
         <v>187</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>175</v>
@@ -2859,7 +3153,7 @@
         <v>187</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>179</v>
@@ -2876,7 +3170,7 @@
         <v>187</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>180</v>
@@ -2893,7 +3187,7 @@
         <v>187</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>181</v>
@@ -2910,7 +3204,7 @@
         <v>187</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>182</v>
@@ -2930,7 +3224,7 @@
         <v>187</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>183</v>
@@ -2947,7 +3241,7 @@
         <v>187</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>185</v>
@@ -2964,10 +3258,1304 @@
         <v>187</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B108" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B109" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A110" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B111" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B112" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B113" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B114" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B115" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B116" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B117" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B118" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B119" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B120" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B122" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B123" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B124" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B125" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B126" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B127" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B128" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B129" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B131" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B132" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B135" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B137" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B138" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B139" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B140" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B141" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B142" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B146" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B148" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B149" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B150" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A151" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B152" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B154" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B155" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B156" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B158" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B159" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B160" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B162" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B165" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B168" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B169" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B171" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B173" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="4"/>
+      <c r="B174" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B176" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B178" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFBEA72-F29A-1E4E-9E13-84C661031942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47C8AF2-F7BC-D144-B4E5-FAFD2F7A3B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="376">
   <si>
     <t>titolo</t>
   </si>
@@ -878,6 +878,276 @@
   </si>
   <si>
     <t>Napoli</t>
+  </si>
+  <si>
+    <t>IMG_2448.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2450.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2453.JPG</t>
+  </si>
+  <si>
+    <t>Pericolo Orsi Polari</t>
+  </si>
+  <si>
+    <t>IMG_2454.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2455.JPG</t>
+  </si>
+  <si>
+    <t>Miniera abbandonata</t>
+  </si>
+  <si>
+    <t>IMG_2458.JPG</t>
+  </si>
+  <si>
+    <t>Renna nel giardino</t>
+  </si>
+  <si>
+    <t>IMG_2459.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2460.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2461.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2463.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2462.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2465.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2467.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2474.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2477.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2480.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2485.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2491.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2492.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2493.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2498.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2506.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2511.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2519.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2525.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2528.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2526.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2531.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2534.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2543.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2546.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2548.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2549.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2564.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2566.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2569.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2571.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2570.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2572.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2574.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2575.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2576.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2577.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2580.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2583.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2584.JPG</t>
+  </si>
+  <si>
+    <t>Pedalata estrema</t>
+  </si>
+  <si>
+    <t>IMG_2586.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2590.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2591.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2592.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2593.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2594.JPG</t>
+  </si>
+  <si>
+    <t>Trova la volpe</t>
+  </si>
+  <si>
+    <t>IMG_2595.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2596.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2597.JPG</t>
+  </si>
+  <si>
+    <t>Husky rumorosi</t>
+  </si>
+  <si>
+    <t>IMG_2598.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2600.JPG</t>
+  </si>
+  <si>
+    <t>Oltre i confini</t>
+  </si>
+  <si>
+    <t>IMG_2605.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2607.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2609.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2611.JPG</t>
+  </si>
+  <si>
+    <t>Occhi di ghiaccio</t>
+  </si>
+  <si>
+    <t>IMG_2613.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2615.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2617.JPG</t>
+  </si>
+  <si>
+    <t>Il bunker dell'apocalisse</t>
+  </si>
+  <si>
+    <t>IMG_2601.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2619.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2622.JPG</t>
+  </si>
+  <si>
+    <t>Volpe artica!</t>
+  </si>
+  <si>
+    <t>IMG_2623.JPG</t>
+  </si>
+  <si>
+    <t>Caccia all'orso</t>
+  </si>
+  <si>
+    <t>IMG_2625.JPG</t>
+  </si>
+  <si>
+    <t>A mali estremi</t>
+  </si>
+  <si>
+    <t>IMG_2626.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2627.JPG</t>
+  </si>
+  <si>
+    <t>Husky cafè</t>
+  </si>
+  <si>
+    <t>IMG_2628.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2630.JPG</t>
+  </si>
+  <si>
+    <t>svalbard</t>
+  </si>
+  <si>
+    <t>orso polare</t>
+  </si>
+  <si>
+    <t>maggio 2026</t>
+  </si>
+  <si>
+    <t>Longyearbyen</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -4558,6 +4828,1303 @@
         <v>283</v>
       </c>
     </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B180" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B181" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B183" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B186" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B187" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B188" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B189" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B190" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B191" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B192" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="193" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B193" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="194" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B194" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="195" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B195" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B196" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="197" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B197" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="198" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B198" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B199" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="200" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B200" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="201" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B201" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="202" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B202" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="203" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B203" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="204" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B204" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B205" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="206" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B206" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="207" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B207" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="208" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B208" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="209" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B209" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="210" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B210" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B211" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B212" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B213" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B214" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="215" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B215" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="216" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B216" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="217" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B217" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="218" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B218" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="219" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B219" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="220" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B220" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="221" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B221" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="222" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B222" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="223" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B223" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="224" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B224" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B225" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A226" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B227" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B228" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B229" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B230" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B231" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A232" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B233" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B234" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A235" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B236" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A237" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B238" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B239" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B240" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B241" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A242" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B243" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B244" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A245" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B246" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A247" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A248" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A249" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B250" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A251" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B252" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B253" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47C8AF2-F7BC-D144-B4E5-FAFD2F7A3B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E931B75B-C941-1D46-9AE9-D297AE62B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cartoline" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="376">
   <si>
     <t>titolo</t>
   </si>
@@ -1553,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G253"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -5038,7 +5038,7 @@
         <v>373</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
@@ -5055,7 +5055,7 @@
         <v>373</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="193" spans="2:7" x14ac:dyDescent="0.2">
@@ -5072,7 +5072,7 @@
         <v>373</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="194" spans="2:7" x14ac:dyDescent="0.2">
@@ -5089,7 +5089,7 @@
         <v>373</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.2">
@@ -5106,7 +5106,7 @@
         <v>373</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="196" spans="2:7" x14ac:dyDescent="0.2">
@@ -5123,7 +5123,7 @@
         <v>373</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="197" spans="2:7" x14ac:dyDescent="0.2">
@@ -5140,7 +5140,7 @@
         <v>373</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.2">
@@ -5157,7 +5157,7 @@
         <v>373</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.2">
@@ -5174,7 +5174,7 @@
         <v>373</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="200" spans="2:7" x14ac:dyDescent="0.2">
@@ -5191,7 +5191,7 @@
         <v>373</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="201" spans="2:7" x14ac:dyDescent="0.2">
@@ -5208,7 +5208,7 @@
         <v>373</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="202" spans="2:7" x14ac:dyDescent="0.2">
@@ -5225,7 +5225,7 @@
         <v>373</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.2">
@@ -5242,7 +5242,7 @@
         <v>373</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.2">
@@ -5259,7 +5259,7 @@
         <v>373</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="205" spans="2:7" x14ac:dyDescent="0.2">
@@ -5276,7 +5276,7 @@
         <v>373</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="206" spans="2:7" x14ac:dyDescent="0.2">
@@ -5293,7 +5293,7 @@
         <v>373</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.2">
@@ -5310,7 +5310,7 @@
         <v>373</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.2">
@@ -5327,7 +5327,7 @@
         <v>373</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="209" spans="2:7" x14ac:dyDescent="0.2">
@@ -5344,7 +5344,7 @@
         <v>373</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="210" spans="2:7" x14ac:dyDescent="0.2">
@@ -5361,7 +5361,7 @@
         <v>373</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211" spans="2:7" x14ac:dyDescent="0.2">
@@ -5378,7 +5378,7 @@
         <v>373</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="212" spans="2:7" x14ac:dyDescent="0.2">
@@ -5395,7 +5395,7 @@
         <v>373</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="2:7" x14ac:dyDescent="0.2">
@@ -5412,7 +5412,7 @@
         <v>373</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" spans="2:7" x14ac:dyDescent="0.2">
@@ -5429,7 +5429,7 @@
         <v>373</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="215" spans="2:7" x14ac:dyDescent="0.2">
@@ -5446,7 +5446,7 @@
         <v>373</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.2">
@@ -5463,7 +5463,7 @@
         <v>373</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="217" spans="2:7" x14ac:dyDescent="0.2">
@@ -5480,7 +5480,7 @@
         <v>373</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="218" spans="2:7" x14ac:dyDescent="0.2">
@@ -5497,7 +5497,7 @@
         <v>373</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="219" spans="2:7" x14ac:dyDescent="0.2">
@@ -5514,7 +5514,7 @@
         <v>373</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="220" spans="2:7" x14ac:dyDescent="0.2">
@@ -5531,7 +5531,7 @@
         <v>373</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="221" spans="2:7" x14ac:dyDescent="0.2">
@@ -5548,7 +5548,7 @@
         <v>373</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="222" spans="2:7" x14ac:dyDescent="0.2">
@@ -5565,7 +5565,7 @@
         <v>373</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="223" spans="2:7" x14ac:dyDescent="0.2">
@@ -5582,7 +5582,7 @@
         <v>373</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="224" spans="2:7" x14ac:dyDescent="0.2">
@@ -5599,10 +5599,13 @@
         <v>373</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A225" s="4" t="s">
+        <v>335</v>
+      </c>
       <c r="B225" s="4" t="s">
         <v>372</v>
       </c>
@@ -5616,13 +5619,10 @@
         <v>373</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A226" s="4" t="s">
-        <v>335</v>
-      </c>
       <c r="B226" s="4" t="s">
         <v>372</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>373</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
@@ -5653,7 +5653,7 @@
         <v>373</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -5670,7 +5670,7 @@
         <v>373</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -5687,7 +5687,7 @@
         <v>373</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
@@ -5704,10 +5704,13 @@
         <v>373</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A231" s="4" t="s">
+        <v>342</v>
+      </c>
       <c r="B231" s="4" t="s">
         <v>372</v>
       </c>
@@ -5721,13 +5724,10 @@
         <v>373</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A232" s="4" t="s">
-        <v>342</v>
-      </c>
       <c r="B232" s="4" t="s">
         <v>372</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>373</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
@@ -5758,10 +5758,13 @@
         <v>373</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A234" s="4" t="s">
+        <v>346</v>
+      </c>
       <c r="B234" s="4" t="s">
         <v>372</v>
       </c>
@@ -5775,13 +5778,10 @@
         <v>373</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A235" s="4" t="s">
-        <v>346</v>
-      </c>
       <c r="B235" s="4" t="s">
         <v>372</v>
       </c>
@@ -5795,10 +5795,13 @@
         <v>373</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A236" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="B236" s="4" t="s">
         <v>372</v>
       </c>
@@ -5812,13 +5815,10 @@
         <v>373</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A237" s="4" t="s">
-        <v>349</v>
-      </c>
       <c r="B237" s="4" t="s">
         <v>372</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>373</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -5849,7 +5849,7 @@
         <v>373</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -5866,7 +5866,7 @@
         <v>373</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -5883,10 +5883,13 @@
         <v>373</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A241" s="4" t="s">
+        <v>354</v>
+      </c>
       <c r="B241" s="4" t="s">
         <v>372</v>
       </c>
@@ -5900,13 +5903,10 @@
         <v>373</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A242" s="4" t="s">
-        <v>354</v>
-      </c>
       <c r="B242" s="4" t="s">
         <v>372</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>373</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
@@ -5937,10 +5937,13 @@
         <v>373</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A244" s="4" t="s">
+        <v>358</v>
+      </c>
       <c r="B244" s="4" t="s">
         <v>372</v>
       </c>
@@ -5954,13 +5957,10 @@
         <v>373</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A245" s="4" t="s">
-        <v>358</v>
-      </c>
       <c r="B245" s="4" t="s">
         <v>372</v>
       </c>
@@ -5974,10 +5974,13 @@
         <v>373</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A246" s="4" t="s">
+        <v>362</v>
+      </c>
       <c r="B246" s="4" t="s">
         <v>372</v>
       </c>
@@ -5991,12 +5994,12 @@
         <v>373</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B247" s="4" t="s">
         <v>372</v>
@@ -6011,12 +6014,12 @@
         <v>373</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>372</v>
@@ -6031,13 +6034,10 @@
         <v>373</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A249" s="4" t="s">
-        <v>366</v>
-      </c>
       <c r="B249" s="4" t="s">
         <v>372</v>
       </c>
@@ -6051,10 +6051,13 @@
         <v>373</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A250" s="4" t="s">
+        <v>369</v>
+      </c>
       <c r="B250" s="4" t="s">
         <v>372</v>
       </c>
@@ -6068,13 +6071,10 @@
         <v>373</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A251" s="4" t="s">
-        <v>369</v>
-      </c>
       <c r="B251" s="4" t="s">
         <v>372</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>373</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
@@ -6105,23 +6105,6 @@
         <v>373</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B253" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D253" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="F253" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="G253" s="2" t="s">
         <v>371</v>
       </c>
     </row>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E931B75B-C941-1D46-9AE9-D297AE62B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61438913-42B8-4840-9F9D-CF62B3E4A007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="523">
   <si>
     <t>titolo</t>
   </si>
@@ -1148,6 +1148,447 @@
   </si>
   <si>
     <t>Longyearbyen</t>
+  </si>
+  <si>
+    <t>Capo Nord</t>
+  </si>
+  <si>
+    <t>giugno 2026</t>
+  </si>
+  <si>
+    <t>renna</t>
+  </si>
+  <si>
+    <t>IMG_2950.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2951.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2953.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2954.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2956.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2957.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2962.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2966.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2967.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2968.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2970.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2971.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2972.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2973.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2975.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2976.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2978.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2981.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2982.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2983.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2985.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2986.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2987.JPG</t>
+  </si>
+  <si>
+    <t>Il binocolo</t>
+  </si>
+  <si>
+    <t>Max ha trovato un binocolo da 700 euro lungo il sentiero</t>
+  </si>
+  <si>
+    <t>IMG_2995.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2997.JPG</t>
+  </si>
+  <si>
+    <t>Saluti da Senja!</t>
+  </si>
+  <si>
+    <t>IMG_2998.JPG</t>
+  </si>
+  <si>
+    <t>IMG_2999.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3001.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3002.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3004.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3006.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3008.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3009.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3012.JPG</t>
+  </si>
+  <si>
+    <t>Pisolino con vista</t>
+  </si>
+  <si>
+    <t>IMG_3013.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3015.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3016.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3018.JPG</t>
+  </si>
+  <si>
+    <t>Parkour!</t>
+  </si>
+  <si>
+    <t>IMG_3019.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3020.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3021.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3022.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3023.JPG</t>
+  </si>
+  <si>
+    <t>Né scendere nè salire</t>
+  </si>
+  <si>
+    <t>IMG_3024.JPG</t>
+  </si>
+  <si>
+    <t>Senja</t>
+  </si>
+  <si>
+    <t>capo nord</t>
+  </si>
+  <si>
+    <t>Oksfjordhamn</t>
+  </si>
+  <si>
+    <t>IMG_3026.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3028.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3029.JPG</t>
+  </si>
+  <si>
+    <t>Prima notte in tenda</t>
+  </si>
+  <si>
+    <t>Siamo stati assaltati dalle zanzare mentre mangiavamo piadine col tonno e bevevamo birra isbjorn</t>
+  </si>
+  <si>
+    <t>IMG_3030.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3031.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3032.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3033.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3036.JPG</t>
+  </si>
+  <si>
+    <t>Guidando tra i fiordi</t>
+  </si>
+  <si>
+    <t>IMG_3037.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3038.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3039.JPG</t>
+  </si>
+  <si>
+    <t>Renne!</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>IMG_3047.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3040.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3049.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3056.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3059.JPG</t>
+  </si>
+  <si>
+    <t>Renna chill</t>
+  </si>
+  <si>
+    <t>IMG_3062.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3064.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3066.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3068.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3069.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3072.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3073.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3074.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3076.JPG</t>
+  </si>
+  <si>
+    <t>Arrivati!</t>
+  </si>
+  <si>
+    <t>IMG_3079.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3080.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3082.JPG</t>
+  </si>
+  <si>
+    <t>Ai confini del mondo</t>
+  </si>
+  <si>
+    <t>IMG_3085.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3086.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3088.JPG</t>
+  </si>
+  <si>
+    <t>Passeggiata tra i ghiacci</t>
+  </si>
+  <si>
+    <t>IMG_3089.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3090.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3091.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3092.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3094.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3096.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3097.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3098.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3099.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3105.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3106.JPG</t>
+  </si>
+  <si>
+    <t>Nordkapp 2026</t>
+  </si>
+  <si>
+    <t>IMG_3107.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3108.JPG</t>
+  </si>
+  <si>
+    <t>Il vero Capo Nord</t>
+  </si>
+  <si>
+    <t>Alta Canyon</t>
+  </si>
+  <si>
+    <t>IMG_3109.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3111.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3114.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3115.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3116.JPG</t>
+  </si>
+  <si>
+    <t>Come attraversiamo?</t>
+  </si>
+  <si>
+    <t>IMG_3119.JPG</t>
+  </si>
+  <si>
+    <t>Il Canyon</t>
+  </si>
+  <si>
+    <t>IMG_3120.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3121.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3122.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3123.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3124.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3125.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3127.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3128.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3131.JPG</t>
+  </si>
+  <si>
+    <t>Olderdalen</t>
+  </si>
+  <si>
+    <t>IMG_3133.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3132.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3135.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3139.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3137.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3141.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3143.JPG</t>
+  </si>
+  <si>
+    <t>Lago Azzurro</t>
+  </si>
+  <si>
+    <t>IMG_3147.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3149.JPG</t>
+  </si>
+  <si>
+    <t>Blaisvatnet</t>
+  </si>
+  <si>
+    <t>IMG_3150.JPG</t>
+  </si>
+  <si>
+    <t>Lavori in corso</t>
+  </si>
+  <si>
+    <t>Tromso</t>
+  </si>
+  <si>
+    <t>IMG_3151.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3154.JPG</t>
+  </si>
+  <si>
+    <t>IMG_3156.JPG</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G368"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -6108,6 +6549,1477 @@
         <v>371</v>
       </c>
     </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B253" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B254" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B255" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B256" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="257" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B257" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="258" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B258" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="259" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B259" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="260" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B260" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="261" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B261" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="262" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B262" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="263" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B263" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="264" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B264" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="265" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B265" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="266" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B266" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="267" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B267" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="268" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B268" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="269" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B269" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="270" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B270" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="271" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B271" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="272" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B272" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B273" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B274" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A275" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B276" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G276" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B277" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D277" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G277" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B278" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B279" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D279" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B280" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B281" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B282" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D282" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B283" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B284" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B285" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D285" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G285" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D286" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B287" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B288" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B289" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A290" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B291" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G291" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B292" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B293" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B294" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A295" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B295" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G295" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B296" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B297" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G297" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B298" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G298" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A299" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G299" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B300" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G300" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B301" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G301" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A302" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G302" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B303" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G303" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A304" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="G304" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B305" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G305" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B306" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G306" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B307" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B308" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G308" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B309" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G309" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B310" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G310" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B311" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="G311" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A312" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B313" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G313" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B314" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G314" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B315" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G315" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B316" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G316" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B317" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G317" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B318" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G318" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B319" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G319" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B320" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G320" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A321" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G321" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A322" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G322" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B323" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G323" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B324" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G324" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B325" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B326" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G326" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A327" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G327" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B328" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G328" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B329" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G329" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B330" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G330" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B331" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G331" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B332" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G332" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B333" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G333" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B334" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G334" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B335" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G335" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B336" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G336" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B337" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G337" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A338" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G338" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A339" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G339" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B340" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G340" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B341" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G341" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B342" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G342" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B343" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G343" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B344" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G344" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A345" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G345" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A346" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G346" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B347" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G347" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B348" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G348" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B349" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G349" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B350" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G350" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B351" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G351" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B352" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G352" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B353" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G353" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B354" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G354" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B355" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G355" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B356" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G356" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B357" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G357" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B358" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="G358" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B359" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G359" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B360" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G360" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B361" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G361" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A362" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G362" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B363" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G363" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B364" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G364" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A365" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G365" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B366" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G366" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B367" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G367" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B368" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G368" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61438913-42B8-4840-9F9D-CF62B3E4A007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24E4553-6213-1B4C-872E-F8BF83A668B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="595">
   <si>
     <t>titolo</t>
   </si>
@@ -1315,6 +1315,135 @@
     <t>capo nord</t>
   </si>
   <si>
+    <t>giugno 2027</t>
+  </si>
+  <si>
+    <t>giugno 2028</t>
+  </si>
+  <si>
+    <t>giugno 2029</t>
+  </si>
+  <si>
+    <t>giugno 2030</t>
+  </si>
+  <si>
+    <t>giugno 2031</t>
+  </si>
+  <si>
+    <t>giugno 2032</t>
+  </si>
+  <si>
+    <t>giugno 2033</t>
+  </si>
+  <si>
+    <t>giugno 2034</t>
+  </si>
+  <si>
+    <t>giugno 2035</t>
+  </si>
+  <si>
+    <t>giugno 2036</t>
+  </si>
+  <si>
+    <t>giugno 2037</t>
+  </si>
+  <si>
+    <t>giugno 2038</t>
+  </si>
+  <si>
+    <t>giugno 2039</t>
+  </si>
+  <si>
+    <t>giugno 2040</t>
+  </si>
+  <si>
+    <t>giugno 2041</t>
+  </si>
+  <si>
+    <t>giugno 2042</t>
+  </si>
+  <si>
+    <t>giugno 2043</t>
+  </si>
+  <si>
+    <t>giugno 2044</t>
+  </si>
+  <si>
+    <t>giugno 2045</t>
+  </si>
+  <si>
+    <t>giugno 2046</t>
+  </si>
+  <si>
+    <t>giugno 2047</t>
+  </si>
+  <si>
+    <t>giugno 2048</t>
+  </si>
+  <si>
+    <t>giugno 2049</t>
+  </si>
+  <si>
+    <t>giugno 2050</t>
+  </si>
+  <si>
+    <t>giugno 2051</t>
+  </si>
+  <si>
+    <t>giugno 2052</t>
+  </si>
+  <si>
+    <t>giugno 2053</t>
+  </si>
+  <si>
+    <t>giugno 2054</t>
+  </si>
+  <si>
+    <t>giugno 2055</t>
+  </si>
+  <si>
+    <t>giugno 2056</t>
+  </si>
+  <si>
+    <t>giugno 2057</t>
+  </si>
+  <si>
+    <t>giugno 2058</t>
+  </si>
+  <si>
+    <t>giugno 2059</t>
+  </si>
+  <si>
+    <t>giugno 2060</t>
+  </si>
+  <si>
+    <t>giugno 2061</t>
+  </si>
+  <si>
+    <t>giugno 2062</t>
+  </si>
+  <si>
+    <t>giugno 2063</t>
+  </si>
+  <si>
+    <t>giugno 2064</t>
+  </si>
+  <si>
+    <t>giugno 2065</t>
+  </si>
+  <si>
+    <t>giugno 2066</t>
+  </si>
+  <si>
+    <t>giugno 2067</t>
+  </si>
+  <si>
+    <t>giugno 2068</t>
+  </si>
+  <si>
+    <t>giugno 2069</t>
+  </si>
+  <si>
     <t>Oksfjordhamn</t>
   </si>
   <si>
@@ -1589,6 +1718,93 @@
   </si>
   <si>
     <t>IMG_3156.JPG</t>
+  </si>
+  <si>
+    <t>giugno 2070</t>
+  </si>
+  <si>
+    <t>giugno 2071</t>
+  </si>
+  <si>
+    <t>giugno 2072</t>
+  </si>
+  <si>
+    <t>giugno 2073</t>
+  </si>
+  <si>
+    <t>giugno 2074</t>
+  </si>
+  <si>
+    <t>giugno 2075</t>
+  </si>
+  <si>
+    <t>giugno 2076</t>
+  </si>
+  <si>
+    <t>giugno 2077</t>
+  </si>
+  <si>
+    <t>giugno 2078</t>
+  </si>
+  <si>
+    <t>giugno 2079</t>
+  </si>
+  <si>
+    <t>giugno 2080</t>
+  </si>
+  <si>
+    <t>giugno 2081</t>
+  </si>
+  <si>
+    <t>giugno 2082</t>
+  </si>
+  <si>
+    <t>giugno 2083</t>
+  </si>
+  <si>
+    <t>giugno 2084</t>
+  </si>
+  <si>
+    <t>giugno 2085</t>
+  </si>
+  <si>
+    <t>giugno 2086</t>
+  </si>
+  <si>
+    <t>giugno 2087</t>
+  </si>
+  <si>
+    <t>giugno 2088</t>
+  </si>
+  <si>
+    <t>giugno 2089</t>
+  </si>
+  <si>
+    <t>giugno 2090</t>
+  </si>
+  <si>
+    <t>giugno 2091</t>
+  </si>
+  <si>
+    <t>giugno 2092</t>
+  </si>
+  <si>
+    <t>giugno 2093</t>
+  </si>
+  <si>
+    <t>giugno 2094</t>
+  </si>
+  <si>
+    <t>giugno 2095</t>
+  </si>
+  <si>
+    <t>giugno 2096</t>
+  </si>
+  <si>
+    <t>giugno 2097</t>
+  </si>
+  <si>
+    <t>giugno 2098</t>
   </si>
 </sst>
 </file>
@@ -7191,10 +7407,13 @@
         <v>430</v>
       </c>
       <c r="C297" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D297" s="4" t="s">
         <v>431</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>432</v>
+        <v>475</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -7202,27 +7421,33 @@
         <v>430</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>432</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>433</v>
+        <v>476</v>
       </c>
     </row>
     <row r="299" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>434</v>
+        <v>477</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -7230,10 +7455,13 @@
         <v>430</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>434</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>437</v>
+        <v>480</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -7241,24 +7469,30 @@
         <v>430</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>435</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
-        <v>446</v>
+        <v>489</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>436</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>439</v>
+        <v>482</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
@@ -7266,24 +7500,30 @@
         <v>430</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="B304" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>431</v>
+        <v>474</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>438</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>441</v>
+        <v>484</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.2">
@@ -7291,10 +7531,13 @@
         <v>430</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>447</v>
+        <v>490</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>443</v>
+        <v>486</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -7302,10 +7545,13 @@
         <v>430</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>447</v>
+        <v>490</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>440</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>444</v>
+        <v>487</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.2">
@@ -7313,10 +7559,13 @@
         <v>430</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>447</v>
+        <v>490</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>441</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>445</v>
+        <v>488</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
@@ -7324,10 +7573,13 @@
         <v>430</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>447</v>
+        <v>490</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>442</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>449</v>
+        <v>492</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.2">
@@ -7335,10 +7587,13 @@
         <v>430</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>447</v>
+        <v>490</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>443</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>448</v>
+        <v>491</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.2">
@@ -7346,10 +7601,13 @@
         <v>430</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>447</v>
+        <v>490</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>444</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>450</v>
+        <v>493</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.2">
@@ -7357,15 +7615,18 @@
         <v>430</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>447</v>
+        <v>490</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>445</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>451</v>
+        <v>494</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>430</v>
@@ -7373,8 +7634,11 @@
       <c r="C312" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D312" s="4" t="s">
+        <v>446</v>
+      </c>
       <c r="G312" s="2" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.2">
@@ -7384,8 +7648,11 @@
       <c r="C313" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D313" s="4" t="s">
+        <v>447</v>
+      </c>
       <c r="G313" s="2" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.2">
@@ -7395,8 +7662,11 @@
       <c r="C314" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D314" s="4" t="s">
+        <v>448</v>
+      </c>
       <c r="G314" s="2" t="s">
-        <v>455</v>
+        <v>498</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.2">
@@ -7406,8 +7676,11 @@
       <c r="C315" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D315" s="4" t="s">
+        <v>449</v>
+      </c>
       <c r="G315" s="2" t="s">
-        <v>456</v>
+        <v>499</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -7417,8 +7690,11 @@
       <c r="C316" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D316" s="4" t="s">
+        <v>450</v>
+      </c>
       <c r="G316" s="2" t="s">
-        <v>457</v>
+        <v>500</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.2">
@@ -7428,8 +7704,11 @@
       <c r="C317" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D317" s="4" t="s">
+        <v>451</v>
+      </c>
       <c r="G317" s="2" t="s">
-        <v>458</v>
+        <v>501</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -7439,8 +7718,11 @@
       <c r="C318" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D318" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="G318" s="2" t="s">
-        <v>459</v>
+        <v>502</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
@@ -7450,8 +7732,11 @@
       <c r="C319" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D319" s="4" t="s">
+        <v>453</v>
+      </c>
       <c r="G319" s="2" t="s">
-        <v>460</v>
+        <v>503</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.2">
@@ -7461,13 +7746,16 @@
       <c r="C320" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D320" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="G320" s="2" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="B321" s="4" t="s">
         <v>430</v>
@@ -7475,13 +7763,16 @@
       <c r="C321" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D321" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="G321" s="2" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
-        <v>467</v>
+        <v>510</v>
       </c>
       <c r="B322" s="4" t="s">
         <v>430</v>
@@ -7489,8 +7780,11 @@
       <c r="C322" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D322" s="4" t="s">
+        <v>456</v>
+      </c>
       <c r="G322" s="2" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.2">
@@ -7500,8 +7794,11 @@
       <c r="C323" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D323" s="4" t="s">
+        <v>457</v>
+      </c>
       <c r="G323" s="2" t="s">
-        <v>465</v>
+        <v>508</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.2">
@@ -7511,8 +7808,11 @@
       <c r="C324" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D324" s="4" t="s">
+        <v>458</v>
+      </c>
       <c r="G324" s="2" t="s">
-        <v>466</v>
+        <v>509</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.2">
@@ -7522,8 +7822,11 @@
       <c r="C325" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D325" s="4" t="s">
+        <v>459</v>
+      </c>
       <c r="G325" s="2" t="s">
-        <v>468</v>
+        <v>511</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
@@ -7533,13 +7836,16 @@
       <c r="C326" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D326" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="G326" s="2" t="s">
-        <v>469</v>
+        <v>512</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="B327" s="4" t="s">
         <v>430</v>
@@ -7547,8 +7853,11 @@
       <c r="C327" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D327" s="4" t="s">
+        <v>461</v>
+      </c>
       <c r="G327" s="2" t="s">
-        <v>470</v>
+        <v>513</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.2">
@@ -7558,8 +7867,11 @@
       <c r="C328" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D328" s="4" t="s">
+        <v>462</v>
+      </c>
       <c r="G328" s="2" t="s">
-        <v>472</v>
+        <v>515</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.2">
@@ -7569,8 +7881,11 @@
       <c r="C329" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D329" s="4" t="s">
+        <v>463</v>
+      </c>
       <c r="G329" s="2" t="s">
-        <v>473</v>
+        <v>516</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.2">
@@ -7580,8 +7895,11 @@
       <c r="C330" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D330" s="4" t="s">
+        <v>464</v>
+      </c>
       <c r="G330" s="2" t="s">
-        <v>474</v>
+        <v>517</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.2">
@@ -7591,8 +7909,11 @@
       <c r="C331" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D331" s="4" t="s">
+        <v>465</v>
+      </c>
       <c r="G331" s="2" t="s">
-        <v>475</v>
+        <v>518</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.2">
@@ -7602,8 +7923,11 @@
       <c r="C332" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D332" s="4" t="s">
+        <v>466</v>
+      </c>
       <c r="G332" s="2" t="s">
-        <v>476</v>
+        <v>519</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.2">
@@ -7613,8 +7937,11 @@
       <c r="C333" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D333" s="4" t="s">
+        <v>467</v>
+      </c>
       <c r="G333" s="2" t="s">
-        <v>477</v>
+        <v>520</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.2">
@@ -7624,8 +7951,11 @@
       <c r="C334" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D334" s="4" t="s">
+        <v>468</v>
+      </c>
       <c r="G334" s="2" t="s">
-        <v>478</v>
+        <v>521</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
@@ -7635,8 +7965,11 @@
       <c r="C335" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D335" s="4" t="s">
+        <v>469</v>
+      </c>
       <c r="G335" s="2" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.2">
@@ -7646,8 +7979,11 @@
       <c r="C336" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D336" s="4" t="s">
+        <v>470</v>
+      </c>
       <c r="G336" s="2" t="s">
-        <v>480</v>
+        <v>523</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.2">
@@ -7657,13 +7993,16 @@
       <c r="C337" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D337" s="4" t="s">
+        <v>471</v>
+      </c>
       <c r="G337" s="2" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="B338" s="4" t="s">
         <v>430</v>
@@ -7671,13 +8010,16 @@
       <c r="C338" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D338" s="4" t="s">
+        <v>472</v>
+      </c>
       <c r="G338" s="2" t="s">
-        <v>482</v>
+        <v>525</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>430</v>
@@ -7685,8 +8027,11 @@
       <c r="C339" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D339" s="4" t="s">
+        <v>473</v>
+      </c>
       <c r="G339" s="2" t="s">
-        <v>484</v>
+        <v>527</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.2">
@@ -7696,8 +8041,11 @@
       <c r="C340" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="D340" s="4" t="s">
+        <v>566</v>
+      </c>
       <c r="G340" s="2" t="s">
-        <v>485</v>
+        <v>528</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
@@ -7705,10 +8053,13 @@
         <v>430</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D341" s="4" t="s">
+        <v>567</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
@@ -7716,10 +8067,13 @@
         <v>430</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>568</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
@@ -7727,10 +8081,13 @@
         <v>430</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D343" s="4" t="s">
+        <v>569</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>490</v>
+        <v>533</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.2">
@@ -7738,38 +8095,47 @@
         <v>430</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D344" s="4" t="s">
+        <v>570</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>491</v>
+        <v>534</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="B345" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D345" s="4" t="s">
+        <v>571</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
-        <v>495</v>
+        <v>538</v>
       </c>
       <c r="B346" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D346" s="4" t="s">
+        <v>572</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>494</v>
+        <v>537</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
@@ -7777,10 +8143,13 @@
         <v>430</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>573</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>496</v>
+        <v>539</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
@@ -7788,10 +8157,13 @@
         <v>430</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>574</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>497</v>
+        <v>540</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
@@ -7799,10 +8171,13 @@
         <v>430</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>575</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>498</v>
+        <v>541</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
@@ -7810,10 +8185,13 @@
         <v>430</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>576</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>499</v>
+        <v>542</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
@@ -7821,10 +8199,13 @@
         <v>430</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D351" s="4" t="s">
+        <v>577</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>500</v>
+        <v>543</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
@@ -7832,10 +8213,13 @@
         <v>430</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>501</v>
+        <v>544</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
@@ -7843,10 +8227,13 @@
         <v>430</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>579</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>502</v>
+        <v>545</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
@@ -7854,10 +8241,13 @@
         <v>430</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>580</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>503</v>
+        <v>546</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
@@ -7865,10 +8255,13 @@
         <v>430</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>487</v>
+        <v>530</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>581</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>504</v>
+        <v>547</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
@@ -7876,10 +8269,13 @@
         <v>430</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>505</v>
+        <v>548</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>582</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>507</v>
+        <v>550</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
@@ -7887,10 +8283,13 @@
         <v>430</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>505</v>
+        <v>548</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>583</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>506</v>
+        <v>549</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
@@ -7898,10 +8297,13 @@
         <v>430</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>505</v>
+        <v>548</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>584</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>508</v>
+        <v>551</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
@@ -7909,10 +8311,13 @@
         <v>430</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>516</v>
+        <v>559</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>585</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>510</v>
+        <v>553</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
@@ -7920,10 +8325,13 @@
         <v>430</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>516</v>
+        <v>559</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>586</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>509</v>
+        <v>552</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
@@ -7931,24 +8339,30 @@
         <v>430</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>516</v>
+        <v>559</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>587</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>511</v>
+        <v>554</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" s="4" t="s">
-        <v>513</v>
+        <v>556</v>
       </c>
       <c r="B362" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>516</v>
+        <v>559</v>
+      </c>
+      <c r="D362" s="4" t="s">
+        <v>588</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>512</v>
+        <v>555</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
@@ -7956,10 +8370,13 @@
         <v>430</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>516</v>
+        <v>559</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>589</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>514</v>
+        <v>557</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
@@ -7967,24 +8384,30 @@
         <v>430</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>516</v>
+        <v>559</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>590</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>515</v>
+        <v>558</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" s="4" t="s">
-        <v>518</v>
+        <v>561</v>
       </c>
       <c r="B365" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>519</v>
+        <v>562</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>591</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>517</v>
+        <v>560</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
@@ -7992,10 +8415,13 @@
         <v>430</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>519</v>
+        <v>562</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>592</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>520</v>
+        <v>563</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
@@ -8003,10 +8429,13 @@
         <v>430</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>519</v>
+        <v>562</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>593</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>521</v>
+        <v>564</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
@@ -8014,10 +8443,13 @@
         <v>430</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>519</v>
+        <v>562</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>594</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>522</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24E4553-6213-1B4C-872E-F8BF83A668B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C318AB76-59A4-3942-9295-70FA1CECE2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="523">
   <si>
     <t>titolo</t>
   </si>
@@ -1315,135 +1315,6 @@
     <t>capo nord</t>
   </si>
   <si>
-    <t>giugno 2027</t>
-  </si>
-  <si>
-    <t>giugno 2028</t>
-  </si>
-  <si>
-    <t>giugno 2029</t>
-  </si>
-  <si>
-    <t>giugno 2030</t>
-  </si>
-  <si>
-    <t>giugno 2031</t>
-  </si>
-  <si>
-    <t>giugno 2032</t>
-  </si>
-  <si>
-    <t>giugno 2033</t>
-  </si>
-  <si>
-    <t>giugno 2034</t>
-  </si>
-  <si>
-    <t>giugno 2035</t>
-  </si>
-  <si>
-    <t>giugno 2036</t>
-  </si>
-  <si>
-    <t>giugno 2037</t>
-  </si>
-  <si>
-    <t>giugno 2038</t>
-  </si>
-  <si>
-    <t>giugno 2039</t>
-  </si>
-  <si>
-    <t>giugno 2040</t>
-  </si>
-  <si>
-    <t>giugno 2041</t>
-  </si>
-  <si>
-    <t>giugno 2042</t>
-  </si>
-  <si>
-    <t>giugno 2043</t>
-  </si>
-  <si>
-    <t>giugno 2044</t>
-  </si>
-  <si>
-    <t>giugno 2045</t>
-  </si>
-  <si>
-    <t>giugno 2046</t>
-  </si>
-  <si>
-    <t>giugno 2047</t>
-  </si>
-  <si>
-    <t>giugno 2048</t>
-  </si>
-  <si>
-    <t>giugno 2049</t>
-  </si>
-  <si>
-    <t>giugno 2050</t>
-  </si>
-  <si>
-    <t>giugno 2051</t>
-  </si>
-  <si>
-    <t>giugno 2052</t>
-  </si>
-  <si>
-    <t>giugno 2053</t>
-  </si>
-  <si>
-    <t>giugno 2054</t>
-  </si>
-  <si>
-    <t>giugno 2055</t>
-  </si>
-  <si>
-    <t>giugno 2056</t>
-  </si>
-  <si>
-    <t>giugno 2057</t>
-  </si>
-  <si>
-    <t>giugno 2058</t>
-  </si>
-  <si>
-    <t>giugno 2059</t>
-  </si>
-  <si>
-    <t>giugno 2060</t>
-  </si>
-  <si>
-    <t>giugno 2061</t>
-  </si>
-  <si>
-    <t>giugno 2062</t>
-  </si>
-  <si>
-    <t>giugno 2063</t>
-  </si>
-  <si>
-    <t>giugno 2064</t>
-  </si>
-  <si>
-    <t>giugno 2065</t>
-  </si>
-  <si>
-    <t>giugno 2066</t>
-  </si>
-  <si>
-    <t>giugno 2067</t>
-  </si>
-  <si>
-    <t>giugno 2068</t>
-  </si>
-  <si>
-    <t>giugno 2069</t>
-  </si>
-  <si>
     <t>Oksfjordhamn</t>
   </si>
   <si>
@@ -1718,93 +1589,6 @@
   </si>
   <si>
     <t>IMG_3156.JPG</t>
-  </si>
-  <si>
-    <t>giugno 2070</t>
-  </si>
-  <si>
-    <t>giugno 2071</t>
-  </si>
-  <si>
-    <t>giugno 2072</t>
-  </si>
-  <si>
-    <t>giugno 2073</t>
-  </si>
-  <si>
-    <t>giugno 2074</t>
-  </si>
-  <si>
-    <t>giugno 2075</t>
-  </si>
-  <si>
-    <t>giugno 2076</t>
-  </si>
-  <si>
-    <t>giugno 2077</t>
-  </si>
-  <si>
-    <t>giugno 2078</t>
-  </si>
-  <si>
-    <t>giugno 2079</t>
-  </si>
-  <si>
-    <t>giugno 2080</t>
-  </si>
-  <si>
-    <t>giugno 2081</t>
-  </si>
-  <si>
-    <t>giugno 2082</t>
-  </si>
-  <si>
-    <t>giugno 2083</t>
-  </si>
-  <si>
-    <t>giugno 2084</t>
-  </si>
-  <si>
-    <t>giugno 2085</t>
-  </si>
-  <si>
-    <t>giugno 2086</t>
-  </si>
-  <si>
-    <t>giugno 2087</t>
-  </si>
-  <si>
-    <t>giugno 2088</t>
-  </si>
-  <si>
-    <t>giugno 2089</t>
-  </si>
-  <si>
-    <t>giugno 2090</t>
-  </si>
-  <si>
-    <t>giugno 2091</t>
-  </si>
-  <si>
-    <t>giugno 2092</t>
-  </si>
-  <si>
-    <t>giugno 2093</t>
-  </si>
-  <si>
-    <t>giugno 2094</t>
-  </si>
-  <si>
-    <t>giugno 2095</t>
-  </si>
-  <si>
-    <t>giugno 2096</t>
-  </si>
-  <si>
-    <t>giugno 2097</t>
-  </si>
-  <si>
-    <t>giugno 2098</t>
   </si>
 </sst>
 </file>
@@ -7407,13 +7191,13 @@
         <v>430</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>431</v>
+        <v>377</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>475</v>
+        <v>432</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
@@ -7421,33 +7205,33 @@
         <v>430</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>476</v>
+        <v>433</v>
       </c>
     </row>
     <row r="299" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
-        <v>478</v>
+        <v>435</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>479</v>
+        <v>436</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>477</v>
+        <v>434</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
@@ -7455,13 +7239,13 @@
         <v>430</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>434</v>
+        <v>377</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>480</v>
+        <v>437</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
@@ -7469,30 +7253,30 @@
         <v>430</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>481</v>
+        <v>438</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
-        <v>489</v>
+        <v>446</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>436</v>
+        <v>377</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>482</v>
+        <v>439</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
@@ -7500,30 +7284,30 @@
         <v>430</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>483</v>
+        <v>440</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
-        <v>485</v>
+        <v>442</v>
       </c>
       <c r="B304" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>438</v>
+        <v>377</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>484</v>
+        <v>441</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.2">
@@ -7531,13 +7315,13 @@
         <v>430</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>439</v>
+        <v>377</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>486</v>
+        <v>443</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -7545,13 +7329,13 @@
         <v>430</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>440</v>
+        <v>377</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>487</v>
+        <v>444</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.2">
@@ -7559,13 +7343,13 @@
         <v>430</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>441</v>
+        <v>377</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>488</v>
+        <v>445</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
@@ -7573,13 +7357,13 @@
         <v>430</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>442</v>
+        <v>377</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>492</v>
+        <v>449</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.2">
@@ -7587,13 +7371,13 @@
         <v>430</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>443</v>
+        <v>377</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.2">
@@ -7601,13 +7385,13 @@
         <v>430</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>493</v>
+        <v>450</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.2">
@@ -7615,18 +7399,18 @@
         <v>430</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>445</v>
+        <v>377</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>494</v>
+        <v>451</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
-        <v>496</v>
+        <v>453</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>430</v>
@@ -7635,10 +7419,10 @@
         <v>376</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>446</v>
+        <v>377</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>495</v>
+        <v>452</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.2">
@@ -7649,10 +7433,10 @@
         <v>376</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>447</v>
+        <v>377</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>497</v>
+        <v>454</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.2">
@@ -7663,10 +7447,10 @@
         <v>376</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>448</v>
+        <v>377</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>498</v>
+        <v>455</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.2">
@@ -7677,10 +7461,10 @@
         <v>376</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>449</v>
+        <v>377</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>499</v>
+        <v>456</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
@@ -7691,10 +7475,10 @@
         <v>376</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>450</v>
+        <v>377</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>500</v>
+        <v>457</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.2">
@@ -7705,10 +7489,10 @@
         <v>376</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>451</v>
+        <v>377</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>501</v>
+        <v>458</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
@@ -7719,10 +7503,10 @@
         <v>376</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>452</v>
+        <v>377</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>502</v>
+        <v>459</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
@@ -7733,10 +7517,10 @@
         <v>376</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>453</v>
+        <v>377</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>503</v>
+        <v>460</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.2">
@@ -7747,15 +7531,15 @@
         <v>376</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>454</v>
+        <v>377</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>504</v>
+        <v>461</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="4" t="s">
-        <v>506</v>
+        <v>463</v>
       </c>
       <c r="B321" s="4" t="s">
         <v>430</v>
@@ -7764,15 +7548,15 @@
         <v>376</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>455</v>
+        <v>377</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>505</v>
+        <v>462</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
-        <v>510</v>
+        <v>467</v>
       </c>
       <c r="B322" s="4" t="s">
         <v>430</v>
@@ -7781,10 +7565,10 @@
         <v>376</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>456</v>
+        <v>377</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>507</v>
+        <v>464</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.2">
@@ -7795,10 +7579,10 @@
         <v>376</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>457</v>
+        <v>377</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>508</v>
+        <v>465</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.2">
@@ -7809,10 +7593,10 @@
         <v>376</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>458</v>
+        <v>377</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>509</v>
+        <v>466</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.2">
@@ -7823,10 +7607,10 @@
         <v>376</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>459</v>
+        <v>377</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>511</v>
+        <v>468</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
@@ -7837,15 +7621,15 @@
         <v>376</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>460</v>
+        <v>377</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>512</v>
+        <v>469</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="B327" s="4" t="s">
         <v>430</v>
@@ -7854,10 +7638,10 @@
         <v>376</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>461</v>
+        <v>377</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>513</v>
+        <v>470</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.2">
@@ -7868,10 +7652,10 @@
         <v>376</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>462</v>
+        <v>377</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>515</v>
+        <v>472</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.2">
@@ -7882,10 +7666,10 @@
         <v>376</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>463</v>
+        <v>377</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>516</v>
+        <v>473</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.2">
@@ -7896,10 +7680,10 @@
         <v>376</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>464</v>
+        <v>377</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>517</v>
+        <v>474</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.2">
@@ -7910,10 +7694,10 @@
         <v>376</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>465</v>
+        <v>377</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>518</v>
+        <v>475</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.2">
@@ -7924,10 +7708,10 @@
         <v>376</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>466</v>
+        <v>377</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>519</v>
+        <v>476</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.2">
@@ -7938,10 +7722,10 @@
         <v>376</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>467</v>
+        <v>377</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>520</v>
+        <v>477</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.2">
@@ -7952,10 +7736,10 @@
         <v>376</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>468</v>
+        <v>377</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>521</v>
+        <v>478</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
@@ -7966,10 +7750,10 @@
         <v>376</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>469</v>
+        <v>377</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>522</v>
+        <v>479</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.2">
@@ -7980,10 +7764,10 @@
         <v>376</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>470</v>
+        <v>377</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>523</v>
+        <v>480</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.2">
@@ -7994,15 +7778,15 @@
         <v>376</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>471</v>
+        <v>377</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>524</v>
+        <v>481</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
-        <v>526</v>
+        <v>483</v>
       </c>
       <c r="B338" s="4" t="s">
         <v>430</v>
@@ -8011,15 +7795,15 @@
         <v>376</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>472</v>
+        <v>377</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>525</v>
+        <v>482</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="4" t="s">
-        <v>529</v>
+        <v>486</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>430</v>
@@ -8028,10 +7812,10 @@
         <v>376</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>473</v>
+        <v>377</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>527</v>
+        <v>484</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.2">
@@ -8042,10 +7826,10 @@
         <v>376</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>566</v>
+        <v>377</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>528</v>
+        <v>485</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
@@ -8053,13 +7837,13 @@
         <v>430</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>567</v>
+        <v>377</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>531</v>
+        <v>488</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
@@ -8067,13 +7851,13 @@
         <v>430</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>568</v>
+        <v>377</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>532</v>
+        <v>489</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
@@ -8081,13 +7865,13 @@
         <v>430</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>569</v>
+        <v>377</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>533</v>
+        <v>490</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.2">
@@ -8095,47 +7879,47 @@
         <v>430</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>570</v>
+        <v>377</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>534</v>
+        <v>491</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A345" s="4" t="s">
-        <v>536</v>
+        <v>493</v>
       </c>
       <c r="B345" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>571</v>
+        <v>377</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>535</v>
+        <v>492</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
-        <v>538</v>
+        <v>495</v>
       </c>
       <c r="B346" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>572</v>
+        <v>377</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>537</v>
+        <v>494</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
@@ -8143,13 +7927,13 @@
         <v>430</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>573</v>
+        <v>377</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>539</v>
+        <v>496</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
@@ -8157,13 +7941,13 @@
         <v>430</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>574</v>
+        <v>377</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>540</v>
+        <v>497</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
@@ -8171,13 +7955,13 @@
         <v>430</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>575</v>
+        <v>377</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>541</v>
+        <v>498</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
@@ -8185,13 +7969,13 @@
         <v>430</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>576</v>
+        <v>377</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>542</v>
+        <v>499</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
@@ -8199,13 +7983,13 @@
         <v>430</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>577</v>
+        <v>377</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>543</v>
+        <v>500</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
@@ -8213,13 +7997,13 @@
         <v>430</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>578</v>
+        <v>377</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>544</v>
+        <v>501</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.2">
@@ -8227,13 +8011,13 @@
         <v>430</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>579</v>
+        <v>377</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>545</v>
+        <v>502</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.2">
@@ -8241,13 +8025,13 @@
         <v>430</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>580</v>
+        <v>377</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>546</v>
+        <v>503</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.2">
@@ -8255,13 +8039,13 @@
         <v>430</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>581</v>
+        <v>377</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>547</v>
+        <v>504</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.2">
@@ -8269,13 +8053,13 @@
         <v>430</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>548</v>
+        <v>505</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>582</v>
+        <v>377</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>550</v>
+        <v>507</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.2">
@@ -8283,13 +8067,13 @@
         <v>430</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>548</v>
+        <v>505</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>583</v>
+        <v>377</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>549</v>
+        <v>506</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.2">
@@ -8297,13 +8081,13 @@
         <v>430</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>548</v>
+        <v>505</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>584</v>
+        <v>377</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>551</v>
+        <v>508</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.2">
@@ -8311,13 +8095,13 @@
         <v>430</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>585</v>
+        <v>377</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>553</v>
+        <v>510</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.2">
@@ -8325,13 +8109,13 @@
         <v>430</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>586</v>
+        <v>377</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>552</v>
+        <v>509</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
@@ -8339,30 +8123,30 @@
         <v>430</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>587</v>
+        <v>377</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>554</v>
+        <v>511</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A362" s="4" t="s">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="B362" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>588</v>
+        <v>377</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>555</v>
+        <v>512</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.2">
@@ -8370,13 +8154,13 @@
         <v>430</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>589</v>
+        <v>377</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>557</v>
+        <v>514</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.2">
@@ -8384,30 +8168,30 @@
         <v>430</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>559</v>
+        <v>516</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>590</v>
+        <v>377</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>558</v>
+        <v>515</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A365" s="4" t="s">
-        <v>561</v>
+        <v>518</v>
       </c>
       <c r="B365" s="4" t="s">
         <v>430</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>591</v>
+        <v>377</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>560</v>
+        <v>517</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.2">
@@ -8415,13 +8199,13 @@
         <v>430</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>592</v>
+        <v>377</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>563</v>
+        <v>520</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.2">
@@ -8429,13 +8213,13 @@
         <v>430</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>593</v>
+        <v>377</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>564</v>
+        <v>521</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.2">
@@ -8443,13 +8227,13 @@
         <v>430</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>594</v>
+        <v>377</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>565</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/cartoline.xlsx
+++ b/cartoline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raffaelebalzano/Documents/Pausilypon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C318AB76-59A4-3942-9295-70FA1CECE2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958C01F5-B0ED-9144-B2CB-76DB730F8916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1946" uniqueCount="523">
   <si>
     <t>titolo</t>
   </si>
@@ -6576,6 +6576,9 @@
       <c r="D254" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F254" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G254" s="2" t="s">
         <v>380</v>
       </c>
@@ -6590,6 +6593,9 @@
       <c r="D255" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F255" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G255" s="2" t="s">
         <v>381</v>
       </c>
@@ -6604,6 +6610,9 @@
       <c r="D256" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F256" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G256" s="2" t="s">
         <v>382</v>
       </c>
@@ -6618,6 +6627,9 @@
       <c r="D257" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F257" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G257" s="2" t="s">
         <v>383</v>
       </c>
@@ -6632,6 +6644,9 @@
       <c r="D258" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F258" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G258" s="2" t="s">
         <v>384</v>
       </c>
@@ -6646,6 +6661,9 @@
       <c r="D259" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F259" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G259" s="2" t="s">
         <v>385</v>
       </c>
@@ -6660,6 +6678,9 @@
       <c r="D260" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F260" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G260" s="2" t="s">
         <v>386</v>
       </c>
@@ -6674,6 +6695,9 @@
       <c r="D261" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F261" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G261" s="2" t="s">
         <v>387</v>
       </c>
@@ -6688,6 +6712,9 @@
       <c r="D262" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F262" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G262" s="2" t="s">
         <v>388</v>
       </c>
@@ -6702,6 +6729,9 @@
       <c r="D263" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F263" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G263" s="2" t="s">
         <v>389</v>
       </c>
@@ -6716,6 +6746,9 @@
       <c r="D264" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F264" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G264" s="2" t="s">
         <v>390</v>
       </c>
@@ -6730,6 +6763,9 @@
       <c r="D265" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F265" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G265" s="2" t="s">
         <v>391</v>
       </c>
@@ -6744,6 +6780,9 @@
       <c r="D266" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F266" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G266" s="2" t="s">
         <v>392</v>
       </c>
@@ -6758,6 +6797,9 @@
       <c r="D267" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F267" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G267" s="2" t="s">
         <v>393</v>
       </c>
@@ -6772,6 +6814,9 @@
       <c r="D268" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F268" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G268" s="2" t="s">
         <v>394</v>
       </c>
@@ -6786,6 +6831,9 @@
       <c r="D269" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F269" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G269" s="2" t="s">
         <v>395</v>
       </c>
@@ -6800,6 +6848,9 @@
       <c r="D270" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F270" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G270" s="2" t="s">
         <v>396</v>
       </c>
@@ -6814,6 +6865,9 @@
       <c r="D271" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F271" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G271" s="2" t="s">
         <v>397</v>
       </c>
@@ -6828,6 +6882,9 @@
       <c r="D272" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F272" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G272" s="2" t="s">
         <v>398</v>
       </c>
@@ -6842,6 +6899,9 @@
       <c r="D273" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F273" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G273" s="2" t="s">
         <v>399</v>
       </c>
@@ -6855,6 +6915,9 @@
       </c>
       <c r="D274" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>400</v>
@@ -6876,6 +6939,9 @@
       <c r="E275" s="5" t="s">
         <v>403</v>
       </c>
+      <c r="F275" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G275" s="2" t="s">
         <v>401</v>
       </c>
@@ -6889,6 +6955,9 @@
       </c>
       <c r="D276" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>404</v>
@@ -6907,6 +6976,9 @@
       <c r="D277" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F277" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G277" s="2" t="s">
         <v>405</v>
       </c>
@@ -6921,6 +6993,9 @@
       <c r="D278" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F278" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G278" s="2" t="s">
         <v>407</v>
       </c>
@@ -6935,6 +7010,9 @@
       <c r="D279" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F279" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G279" s="2" t="s">
         <v>408</v>
       </c>
@@ -6949,6 +7027,9 @@
       <c r="D280" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F280" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G280" s="2" t="s">
         <v>409</v>
       </c>
@@ -6963,6 +7044,9 @@
       <c r="D281" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F281" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G281" s="2" t="s">
         <v>410</v>
       </c>
@@ -6977,6 +7061,9 @@
       <c r="D282" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F282" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G282" s="2" t="s">
         <v>411</v>
       </c>
@@ -6991,6 +7078,9 @@
       <c r="D283" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F283" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G283" s="2" t="s">
         <v>412</v>
       </c>
@@ -7005,6 +7095,9 @@
       <c r="D284" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F284" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G284" s="2" t="s">
         <v>413</v>
       </c>
@@ -7018,6 +7111,9 @@
       </c>
       <c r="D285" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>414</v>
@@ -7036,6 +7132,9 @@
       <c r="D286" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F286" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G286" s="2" t="s">
         <v>415</v>
       </c>
@@ -7050,6 +7149,9 @@
       <c r="D287" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F287" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G287" s="2" t="s">
         <v>417</v>
       </c>
@@ -7064,6 +7166,9 @@
       <c r="D288" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F288" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G288" s="2" t="s">
         <v>418</v>
       </c>
@@ -7077,6 +7182,9 @@
       </c>
       <c r="D289" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>419</v>
@@ -7095,6 +7203,9 @@
       <c r="D290" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F290" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G290" s="2" t="s">
         <v>420</v>
       </c>
@@ -7109,6 +7220,9 @@
       <c r="D291" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F291" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G291" s="2" t="s">
         <v>422</v>
       </c>
@@ -7123,6 +7237,9 @@
       <c r="D292" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F292" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G292" s="2" t="s">
         <v>423</v>
       </c>
@@ -7137,6 +7254,9 @@
       <c r="D293" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F293" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G293" s="2" t="s">
         <v>424</v>
       </c>
@@ -7150,6 +7270,9 @@
       </c>
       <c r="D294" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>425</v>
@@ -7168,6 +7291,9 @@
       <c r="D295" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F295" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G295" s="2" t="s">
         <v>426</v>
       </c>
@@ -7182,6 +7308,9 @@
       <c r="D296" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F296" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G296" s="2" t="s">
         <v>428</v>
       </c>
@@ -7196,6 +7325,9 @@
       <c r="D297" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F297" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G297" s="2" t="s">
         <v>432</v>
       </c>
@@ -7209,6 +7341,9 @@
       </c>
       <c r="D298" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>433</v>
@@ -7230,6 +7365,9 @@
       <c r="E299" s="5" t="s">
         <v>436</v>
       </c>
+      <c r="F299" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G299" s="2" t="s">
         <v>434</v>
       </c>
@@ -7244,6 +7382,9 @@
       <c r="D300" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F300" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G300" s="2" t="s">
         <v>437</v>
       </c>
@@ -7257,6 +7398,9 @@
       </c>
       <c r="D301" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>438</v>
@@ -7275,6 +7419,9 @@
       <c r="D302" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F302" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G302" s="2" t="s">
         <v>439</v>
       </c>
@@ -7288,6 +7435,9 @@
       </c>
       <c r="D303" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>440</v>
@@ -7306,6 +7456,9 @@
       <c r="D304" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F304" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G304" s="2" t="s">
         <v>441</v>
       </c>
@@ -7320,6 +7473,9 @@
       <c r="D305" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F305" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G305" s="2" t="s">
         <v>443</v>
       </c>
@@ -7334,6 +7490,9 @@
       <c r="D306" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F306" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G306" s="2" t="s">
         <v>444</v>
       </c>
@@ -7348,6 +7507,9 @@
       <c r="D307" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F307" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G307" s="2" t="s">
         <v>445</v>
       </c>
@@ -7362,6 +7524,9 @@
       <c r="D308" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F308" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G308" s="2" t="s">
         <v>449</v>
       </c>
@@ -7376,6 +7541,9 @@
       <c r="D309" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F309" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G309" s="2" t="s">
         <v>448</v>
       </c>
@@ -7390,6 +7558,9 @@
       <c r="D310" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F310" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G310" s="2" t="s">
         <v>450</v>
       </c>
@@ -7403,6 +7574,9 @@
       </c>
       <c r="D311" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>451</v>
@@ -7421,6 +7595,9 @@
       <c r="D312" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F312" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G312" s="2" t="s">
         <v>452</v>
       </c>
@@ -7435,6 +7612,9 @@
       <c r="D313" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F313" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G313" s="2" t="s">
         <v>454</v>
       </c>
@@ -7449,6 +7629,9 @@
       <c r="D314" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F314" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G314" s="2" t="s">
         <v>455</v>
       </c>
@@ -7463,6 +7646,9 @@
       <c r="D315" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F315" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G315" s="2" t="s">
         <v>456</v>
       </c>
@@ -7477,6 +7663,9 @@
       <c r="D316" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F316" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G316" s="2" t="s">
         <v>457</v>
       </c>
@@ -7491,6 +7680,9 @@
       <c r="D317" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F317" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G317" s="2" t="s">
         <v>458</v>
       </c>
@@ -7505,6 +7697,9 @@
       <c r="D318" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F318" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G318" s="2" t="s">
         <v>459</v>
       </c>
@@ -7519,6 +7714,9 @@
       <c r="D319" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F319" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G319" s="2" t="s">
         <v>460</v>
       </c>
@@ -7532,6 +7730,9 @@
       </c>
       <c r="D320" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>461</v>
@@ -7550,6 +7751,9 @@
       <c r="D321" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F321" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G321" s="2" t="s">
         <v>462</v>
       </c>
@@ -7567,6 +7771,9 @@
       <c r="D322" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F322" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G322" s="2" t="s">
         <v>464</v>
       </c>
@@ -7581,6 +7788,9 @@
       <c r="D323" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F323" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G323" s="2" t="s">
         <v>465</v>
       </c>
@@ -7595,6 +7805,9 @@
       <c r="D324" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F324" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G324" s="2" t="s">
         <v>466</v>
       </c>
@@ -7609,6 +7822,9 @@
       <c r="D325" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F325" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G325" s="2" t="s">
         <v>468</v>
       </c>
@@ -7622,6 +7838,9 @@
       </c>
       <c r="D326" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>469</v>
@@ -7640,6 +7859,9 @@
       <c r="D327" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F327" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G327" s="2" t="s">
         <v>470</v>
       </c>
@@ -7654,6 +7876,9 @@
       <c r="D328" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F328" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G328" s="2" t="s">
         <v>472</v>
       </c>
@@ -7668,6 +7893,9 @@
       <c r="D329" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F329" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G329" s="2" t="s">
         <v>473</v>
       </c>
@@ -7682,6 +7910,9 @@
       <c r="D330" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F330" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G330" s="2" t="s">
         <v>474</v>
       </c>
@@ -7696,6 +7927,9 @@
       <c r="D331" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F331" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G331" s="2" t="s">
         <v>475</v>
       </c>
@@ -7710,6 +7944,9 @@
       <c r="D332" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F332" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G332" s="2" t="s">
         <v>476</v>
       </c>
@@ -7724,6 +7961,9 @@
       <c r="D333" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F333" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G333" s="2" t="s">
         <v>477</v>
       </c>
@@ -7738,6 +7978,9 @@
       <c r="D334" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F334" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G334" s="2" t="s">
         <v>478</v>
       </c>
@@ -7752,6 +7995,9 @@
       <c r="D335" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F335" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G335" s="2" t="s">
         <v>479</v>
       </c>
@@ -7766,6 +8012,9 @@
       <c r="D336" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F336" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G336" s="2" t="s">
         <v>480</v>
       </c>
@@ -7779,6 +8028,9 @@
       </c>
       <c r="D337" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>481</v>
@@ -7797,6 +8049,9 @@
       <c r="D338" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F338" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G338" s="2" t="s">
         <v>482</v>
       </c>
@@ -7814,6 +8069,9 @@
       <c r="D339" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F339" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G339" s="2" t="s">
         <v>484</v>
       </c>
@@ -7828,6 +8086,9 @@
       <c r="D340" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F340" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G340" s="2" t="s">
         <v>485</v>
       </c>
@@ -7842,6 +8103,9 @@
       <c r="D341" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F341" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G341" s="2" t="s">
         <v>488</v>
       </c>
@@ -7856,6 +8120,9 @@
       <c r="D342" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F342" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G342" s="2" t="s">
         <v>489</v>
       </c>
@@ -7870,6 +8137,9 @@
       <c r="D343" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F343" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G343" s="2" t="s">
         <v>490</v>
       </c>
@@ -7883,6 +8153,9 @@
       </c>
       <c r="D344" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>491</v>
@@ -7901,6 +8174,9 @@
       <c r="D345" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F345" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G345" s="2" t="s">
         <v>492</v>
       </c>
@@ -7918,6 +8194,9 @@
       <c r="D346" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F346" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G346" s="2" t="s">
         <v>494</v>
       </c>
@@ -7932,6 +8211,9 @@
       <c r="D347" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F347" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G347" s="2" t="s">
         <v>496</v>
       </c>
@@ -7946,6 +8228,9 @@
       <c r="D348" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F348" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G348" s="2" t="s">
         <v>497</v>
       </c>
@@ -7960,6 +8245,9 @@
       <c r="D349" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F349" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G349" s="2" t="s">
         <v>498</v>
       </c>
@@ -7974,6 +8262,9 @@
       <c r="D350" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F350" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G350" s="2" t="s">
         <v>499</v>
       </c>
@@ -7988,6 +8279,9 @@
       <c r="D351" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F351" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G351" s="2" t="s">
         <v>500</v>
       </c>
@@ -8002,6 +8296,9 @@
       <c r="D352" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F352" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G352" s="2" t="s">
         <v>501</v>
       </c>
@@ -8016,6 +8313,9 @@
       <c r="D353" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F353" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G353" s="2" t="s">
         <v>502</v>
       </c>
@@ -8030,6 +8330,9 @@
       <c r="D354" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F354" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G354" s="2" t="s">
         <v>503</v>
       </c>
@@ -8044,6 +8347,9 @@
       <c r="D355" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F355" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G355" s="2" t="s">
         <v>504</v>
       </c>
@@ -8058,6 +8364,9 @@
       <c r="D356" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F356" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G356" s="2" t="s">
         <v>507</v>
       </c>
@@ -8072,6 +8381,9 @@
       <c r="D357" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F357" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G357" s="2" t="s">
         <v>506</v>
       </c>
@@ -8086,6 +8398,9 @@
       <c r="D358" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F358" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G358" s="2" t="s">
         <v>508</v>
       </c>
@@ -8100,6 +8415,9 @@
       <c r="D359" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F359" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G359" s="2" t="s">
         <v>510</v>
       </c>
@@ -8114,6 +8432,9 @@
       <c r="D360" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F360" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G360" s="2" t="s">
         <v>509</v>
       </c>
@@ -8127,6 +8448,9 @@
       </c>
       <c r="D361" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>511</v>
@@ -8145,6 +8469,9 @@
       <c r="D362" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F362" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G362" s="2" t="s">
         <v>512</v>
       </c>
@@ -8159,6 +8486,9 @@
       <c r="D363" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F363" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G363" s="2" t="s">
         <v>514</v>
       </c>
@@ -8172,6 +8502,9 @@
       </c>
       <c r="D364" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>515</v>
@@ -8190,6 +8523,9 @@
       <c r="D365" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F365" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G365" s="2" t="s">
         <v>517</v>
       </c>
@@ -8204,6 +8540,9 @@
       <c r="D366" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F366" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G366" s="2" t="s">
         <v>520</v>
       </c>
@@ -8218,6 +8557,9 @@
       <c r="D367" s="4" t="s">
         <v>377</v>
       </c>
+      <c r="F367" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="G367" s="2" t="s">
         <v>521</v>
       </c>
@@ -8231,6 +8573,9 @@
       </c>
       <c r="D368" s="4" t="s">
         <v>377</v>
+      </c>
+      <c r="F368" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>522</v>
